--- a/doc/S15称重库协议20250716.xlsx
+++ b/doc/S15称重库协议20250716.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SW15指令" sheetId="1" r:id="rId1"/>
@@ -204,6 +204,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">5AA5000C </t>
     </r>
     <r>
@@ -242,6 +249,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>5AA5000CE13200</t>
     </r>
     <r>
@@ -1414,17 +1428,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
+      <b/>
       <sz val="11"/>
-      <color theme="5"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <strike/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="5"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1972,47 +1986,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2558,7 +2572,7 @@
     <col min="9" max="9" width="87.875" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" ht="41" customHeight="1" spans="1:9">
+    <row r="1" s="6" customFormat="1" ht="41" customHeight="1" spans="1:11">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2569,9 +2583,9 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
-      <c r="I1" s="32"/>
-    </row>
-    <row r="2" s="6" customFormat="1" ht="43" customHeight="1" spans="1:9">
+      <c r="I1" s="21"/>
+    </row>
+    <row r="2" s="6" customFormat="1" ht="43" customHeight="1" spans="1:11">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -2594,162 +2608,162 @@
       <c r="H2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="21" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1" spans="1:9">
-      <c r="A3" s="21">
+    <row r="3" ht="25" customHeight="1" spans="1:11">
+      <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="33"/>
-    </row>
-    <row r="4" ht="25" customHeight="1" spans="1:9">
-      <c r="A4" s="21">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="24"/>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:11">
+      <c r="A4" s="22">
         <v>2</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="33" t="s">
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="24" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="25" customHeight="1" spans="1:9">
-      <c r="A5" s="21">
+    <row r="5" ht="25" customHeight="1" spans="1:11">
+      <c r="A5" s="22">
         <v>3</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="33" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="24" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" ht="25" customHeight="1" spans="1:9">
-      <c r="A6" s="21">
+    <row r="6" ht="25" customHeight="1" spans="1:11">
+      <c r="A6" s="22">
         <v>4</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="33" t="s">
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" ht="25" customHeight="1" spans="1:9">
-      <c r="A7" s="23">
+    <row r="7" ht="25" customHeight="1" spans="1:11">
+      <c r="A7" s="25">
         <v>5</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="33" t="s">
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" ht="25" customHeight="1" spans="1:9">
-      <c r="A8" s="23"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="21" t="s">
+    <row r="8" ht="25" customHeight="1" spans="1:11">
+      <c r="A8" s="25"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="33"/>
-    </row>
-    <row r="9" ht="25" customHeight="1" spans="1:9">
-      <c r="A9" s="23">
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="24"/>
+    </row>
+    <row r="9" ht="25" customHeight="1" spans="1:11">
+      <c r="A9" s="25">
         <v>6</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="33" t="s">
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" ht="25" customHeight="1" spans="1:9">
-      <c r="A10" s="23"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="21" t="s">
+    <row r="10" ht="25" customHeight="1" spans="1:11">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="33"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="24"/>
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:11">
-      <c r="A11" s="21">
+      <c r="A11" s="22">
         <v>7</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="33" t="s">
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="24" t="s">
         <v>29</v>
       </c>
       <c r="J11">
@@ -2759,305 +2773,305 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" ht="25" customHeight="1" spans="1:9">
-      <c r="A12" s="21">
+    <row r="12" ht="25" customHeight="1" spans="1:11">
+      <c r="A12" s="22">
         <v>8</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="33" t="s">
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" ht="25" customHeight="1" spans="1:9">
-      <c r="A13" s="27">
+    <row r="13" ht="25" customHeight="1" spans="1:11">
+      <c r="A13" s="29">
         <v>9</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="34" t="s">
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" ht="25" customHeight="1" spans="1:9">
-      <c r="A14" s="30"/>
-      <c r="B14" s="31" t="s">
+    <row r="14" ht="25" customHeight="1" spans="1:11">
+      <c r="A14" s="33"/>
+      <c r="B14" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="34">
         <v>0</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="31" t="s">
+      <c r="H14" s="34" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="35" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="25" customHeight="1" spans="1:9">
-      <c r="A15" s="30"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31" t="s">
+    <row r="15" ht="25" customHeight="1" spans="1:11">
+      <c r="A15" s="33"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="34">
         <v>1</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="31"/>
-    </row>
-    <row r="16" ht="25" customHeight="1" spans="1:9">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31">
+      <c r="I15" s="34"/>
+    </row>
+    <row r="16" ht="25" customHeight="1" spans="1:11">
+      <c r="A16" s="33"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34">
         <v>2</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="35"/>
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:9">
-      <c r="A17" s="30"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31">
+      <c r="A17" s="33"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34">
         <v>3</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="35"/>
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:9">
-      <c r="A18" s="30"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31">
+      <c r="A18" s="33"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34">
         <v>4</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="35"/>
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:9">
-      <c r="A19" s="30"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="35"/>
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:9">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31" t="s">
+      <c r="A20" s="33"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="35"/>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:9">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31" t="s">
+      <c r="A21" s="33"/>
+      <c r="B21" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="34">
         <v>5</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="31" t="s">
+      <c r="H21" s="34" t="s">
         <v>56</v>
       </c>
       <c r="I21" s="35"/>
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:9">
-      <c r="A22" s="30"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31" t="s">
+      <c r="A22" s="33"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="34">
         <v>6</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H22" s="31" t="s">
+      <c r="H22" s="34" t="s">
         <v>59</v>
       </c>
       <c r="I22" s="35"/>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:9">
-      <c r="A23" s="30"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31">
+      <c r="A23" s="33"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34">
         <v>7</v>
       </c>
-      <c r="F23" s="31" t="s">
+      <c r="F23" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
       <c r="I23" s="35"/>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:9">
-      <c r="A24" s="30"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31">
+      <c r="A24" s="33"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34">
         <v>8</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
       <c r="I24" s="35"/>
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:9">
-      <c r="A25" s="30"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31">
+      <c r="A25" s="33"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34">
         <v>9</v>
       </c>
-      <c r="F25" s="31" t="s">
+      <c r="F25" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
       <c r="I25" s="35"/>
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:9">
-      <c r="A26" s="30"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31" t="s">
+      <c r="A26" s="33"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
       <c r="I26" s="35" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:9">
-      <c r="A27" s="30"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31" t="s">
+      <c r="A27" s="33"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
       <c r="I27" s="35" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:9">
-      <c r="A28" s="23"/>
-      <c r="B28" s="31" t="s">
+      <c r="A28" s="25"/>
+      <c r="B28" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="28">
         <v>10</v>
       </c>
-      <c r="F28" s="26" t="s">
+      <c r="F28" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="34" t="s">
         <v>71</v>
       </c>
       <c r="I28" s="35" t="s">
@@ -3065,912 +3079,912 @@
       </c>
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:9">
-      <c r="A29" s="23"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26" t="s">
+      <c r="A29" s="25"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="28">
         <v>11</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="34" t="s">
         <v>75</v>
       </c>
       <c r="I29" s="35"/>
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:9">
-      <c r="A30" s="23"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26">
+      <c r="A30" s="25"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28">
         <v>12</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
       <c r="I30" s="35"/>
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:9">
-      <c r="A31" s="23"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26">
+      <c r="A31" s="25"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28">
         <v>13</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
       <c r="I31" s="35"/>
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:9">
-      <c r="A32" s="23"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26">
+      <c r="A32" s="25"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28">
         <v>14</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="F32" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
       <c r="I32" s="35"/>
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:9">
-      <c r="A33" s="23"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="26" t="s">
+      <c r="A33" s="25"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
       <c r="I33" s="35" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:9">
-      <c r="A34" s="23"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="26" t="s">
+      <c r="A34" s="25"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
       <c r="I34" s="35" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:9">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21" t="s">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="28">
         <v>15</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="F35" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H35" s="31" t="s">
+      <c r="H35" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I35" s="33" t="s">
+      <c r="I35" s="24" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:9">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26" t="s">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="28">
         <v>16</v>
       </c>
-      <c r="F36" s="26" t="s">
+      <c r="F36" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H36" s="31" t="s">
+      <c r="H36" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I36" s="33"/>
+      <c r="I36" s="24"/>
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:9">
-      <c r="A37" s="21"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28">
         <v>17</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="33"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="24"/>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:9">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28">
         <v>18</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="F38" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="33"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="24"/>
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:9">
-      <c r="A39" s="21"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28">
         <v>19</v>
       </c>
-      <c r="F39" s="26" t="s">
+      <c r="F39" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="33"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="24"/>
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:9">
-      <c r="A40" s="21"/>
-      <c r="B40" s="21" t="s">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="33">
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="24">
         <v>2</v>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:9">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21" t="s">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="33">
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="24">
         <v>3</v>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:9">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21" t="s">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="28">
         <v>20</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="F42" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="G42" s="31" t="s">
+      <c r="G42" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H42" s="31" t="s">
+      <c r="H42" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I42" s="33" t="s">
+      <c r="I42" s="24" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:9">
-      <c r="A43" s="21"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21" t="s">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="28">
         <v>21</v>
       </c>
-      <c r="F43" s="21" t="s">
+      <c r="F43" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G43" s="31" t="s">
+      <c r="G43" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H43" s="31" t="s">
+      <c r="H43" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I43" s="33">
+      <c r="I43" s="24">
         <v>2</v>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:9">
-      <c r="A44" s="21"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21" t="s">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="21"/>
-      <c r="E44" s="26">
+      <c r="D44" s="22"/>
+      <c r="E44" s="28">
         <v>22</v>
       </c>
-      <c r="F44" s="21" t="s">
+      <c r="F44" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="33">
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:9">
-      <c r="A45" s="21"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="26">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="28">
         <v>23</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="F45" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="33"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="24"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:9">
-      <c r="A46" s="21"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="26">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="28">
         <v>24</v>
       </c>
-      <c r="F46" s="21" t="s">
+      <c r="F46" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="33"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="24"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:9">
-      <c r="A47" s="21"/>
-      <c r="B47" s="21" t="s">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="31" t="s">
+      <c r="C47" s="22"/>
+      <c r="D47" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="28">
         <v>25</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F47" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H47" s="31" t="s">
+      <c r="H47" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="I47" s="33"/>
+      <c r="I47" s="24"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:9">
-      <c r="A48" s="21"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21" t="s">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="28">
         <v>26</v>
       </c>
-      <c r="F48" s="21" t="s">
+      <c r="F48" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="G48" s="31" t="s">
+      <c r="G48" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="31" t="s">
+      <c r="H48" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="I48" s="33"/>
+      <c r="I48" s="24"/>
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:9">
-      <c r="A49" s="21"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="26">
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="28">
         <v>27</v>
       </c>
-      <c r="F49" s="21" t="s">
+      <c r="F49" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="33"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="24"/>
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:9">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="26">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="28">
         <v>28</v>
       </c>
-      <c r="F50" s="21" t="s">
+      <c r="F50" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="33"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="24"/>
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:9">
-      <c r="A51" s="21"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="26">
+      <c r="A51" s="22"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="28">
         <v>29</v>
       </c>
-      <c r="F51" s="21" t="s">
+      <c r="F51" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="33"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="24"/>
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:9">
-      <c r="A52" s="21"/>
-      <c r="B52" s="21" t="s">
+      <c r="A52" s="22"/>
+      <c r="B52" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="C52" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D52" s="31" t="s">
+      <c r="D52" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="E52" s="26">
+      <c r="E52" s="28">
         <v>30</v>
       </c>
-      <c r="F52" s="21" t="s">
+      <c r="F52" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="G52" s="31" t="s">
+      <c r="G52" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H52" s="31" t="s">
+      <c r="H52" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="I52" s="33" t="s">
+      <c r="I52" s="24" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="53" ht="25" customHeight="1" spans="1:8">
-      <c r="A53" s="21"/>
-      <c r="B53" s="21"/>
+    <row r="53" ht="25" customHeight="1" spans="1:9">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
       <c r="D53" t="s">
         <v>127</v>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="28">
         <v>31</v>
       </c>
-      <c r="F53" s="21" t="s">
+      <c r="F53" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="G53" s="31" t="s">
+      <c r="G53" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H53" s="31" t="s">
+      <c r="H53" s="34" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="54" ht="25" customHeight="1" spans="1:7">
-      <c r="A54" s="21"/>
-      <c r="B54" s="21"/>
-      <c r="E54" s="26">
+    <row r="54" ht="25" customHeight="1" spans="1:9">
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="E54" s="28">
         <v>32</v>
       </c>
-      <c r="F54" s="21" t="s">
+      <c r="F54" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="G54" s="21"/>
+      <c r="G54" s="22"/>
     </row>
     <row r="55" ht="25" customHeight="1" spans="1:9">
-      <c r="A55" s="21"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="26">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="28">
         <v>33</v>
       </c>
-      <c r="F55" s="21" t="s">
+      <c r="F55" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="33"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" ht="25" customHeight="1" spans="1:9">
-      <c r="A56" s="21"/>
-      <c r="B56" s="21"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="26">
+      <c r="A56" s="22"/>
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="28">
         <v>34</v>
       </c>
-      <c r="F56" s="21" t="s">
+      <c r="F56" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="G56" s="21"/>
-      <c r="H56" s="21"/>
-      <c r="I56" s="33"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="24"/>
     </row>
     <row r="57" ht="25" customHeight="1" spans="1:9">
-      <c r="A57" s="21"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="21" t="s">
+      <c r="A57" s="22"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="D57" s="21"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="33">
+      <c r="D57" s="22"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1" spans="1:9">
-      <c r="A58" s="21"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21" t="s">
+      <c r="A58" s="22"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D58" s="21"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="33">
+      <c r="D58" s="22"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1" spans="1:9">
-      <c r="A59" s="21"/>
-      <c r="B59" s="21" t="s">
+      <c r="A59" s="22"/>
+      <c r="B59" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="C59" s="21"/>
-      <c r="D59" s="31" t="s">
+      <c r="C59" s="22"/>
+      <c r="D59" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="28">
         <v>35</v>
       </c>
-      <c r="F59" s="21" t="s">
+      <c r="F59" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="G59" s="31" t="s">
+      <c r="G59" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H59" s="31" t="s">
+      <c r="H59" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="I59" s="33" t="s">
+      <c r="I59" s="24" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1" spans="1:9">
-      <c r="A60" s="21"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="21" t="s">
+      <c r="A60" s="22"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="E60" s="26">
+      <c r="E60" s="28">
         <v>36</v>
       </c>
-      <c r="F60" s="21" t="s">
+      <c r="F60" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="G60" s="31" t="s">
+      <c r="G60" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H60" s="31" t="s">
+      <c r="H60" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="I60" s="33"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" ht="25" customHeight="1" spans="1:9">
-      <c r="A61" s="21"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="21"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="26">
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="28">
         <v>37</v>
       </c>
-      <c r="F61" s="21" t="s">
+      <c r="F61" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="G61" s="21"/>
-      <c r="H61" s="21"/>
-      <c r="I61" s="33"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="24"/>
     </row>
     <row r="62" ht="25" customHeight="1" spans="1:9">
-      <c r="A62" s="21"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="26">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="28">
         <v>38</v>
       </c>
-      <c r="F62" s="21" t="s">
+      <c r="F62" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="33"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" ht="25" customHeight="1" spans="1:9">
-      <c r="A63" s="21"/>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="26">
+      <c r="A63" s="22"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="28">
         <v>39</v>
       </c>
-      <c r="F63" s="21" t="s">
+      <c r="F63" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="33"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="24"/>
     </row>
     <row r="64" ht="25" customHeight="1" spans="1:9">
-      <c r="A64" s="21"/>
-      <c r="B64" s="21" t="s">
+      <c r="A64" s="22"/>
+      <c r="B64" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="31" t="s">
+      <c r="C64" s="22"/>
+      <c r="D64" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="E64" s="26">
+      <c r="E64" s="28">
         <v>40</v>
       </c>
-      <c r="F64" s="21" t="s">
+      <c r="F64" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="G64" s="31" t="s">
+      <c r="G64" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H64" s="31" t="s">
+      <c r="H64" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="I64" s="33" t="s">
+      <c r="I64" s="24" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1" spans="1:9">
-      <c r="A65" s="21"/>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21" t="s">
+      <c r="A65" s="22"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="E65" s="26">
+      <c r="E65" s="28">
         <v>41</v>
       </c>
-      <c r="F65" s="21" t="s">
+      <c r="F65" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="G65" s="31" t="s">
+      <c r="G65" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H65" s="31" t="s">
+      <c r="H65" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="I65" s="33"/>
+      <c r="I65" s="24"/>
     </row>
     <row r="66" ht="25" customHeight="1" spans="1:9">
-      <c r="A66" s="21"/>
-      <c r="B66" s="21"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="26">
+      <c r="A66" s="22"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="28">
         <v>42</v>
       </c>
-      <c r="F66" s="21" t="s">
+      <c r="F66" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
-      <c r="I66" s="33"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+      <c r="I66" s="24"/>
     </row>
     <row r="67" ht="25" customHeight="1" spans="1:9">
-      <c r="A67" s="21"/>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="26">
+      <c r="A67" s="22"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="28">
         <v>43</v>
       </c>
-      <c r="F67" s="21" t="s">
+      <c r="F67" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
-      <c r="I67" s="33"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="24"/>
     </row>
     <row r="68" ht="25" customHeight="1" spans="1:9">
-      <c r="A68" s="21"/>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="26">
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="28">
         <v>44</v>
       </c>
-      <c r="F68" s="21" t="s">
+      <c r="F68" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="33"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="24"/>
     </row>
     <row r="69" ht="25" customHeight="1" spans="1:9">
-      <c r="A69" s="21"/>
-      <c r="B69" s="21" t="s">
+      <c r="A69" s="22"/>
+      <c r="B69" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="31" t="s">
+      <c r="C69" s="22"/>
+      <c r="D69" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="E69" s="26">
+      <c r="E69" s="28">
         <v>45</v>
       </c>
-      <c r="F69" s="21" t="s">
+      <c r="F69" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="G69" s="31" t="s">
+      <c r="G69" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H69" s="31" t="s">
+      <c r="H69" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="I69" s="33" t="s">
+      <c r="I69" s="24" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="70" ht="25" customHeight="1" spans="1:9">
-      <c r="A70" s="21"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21" t="s">
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="E70" s="26">
+      <c r="E70" s="28">
         <v>46</v>
       </c>
-      <c r="F70" s="21" t="s">
+      <c r="F70" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="G70" s="31" t="s">
+      <c r="G70" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H70" s="31" t="s">
+      <c r="H70" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="I70" s="33"/>
+      <c r="I70" s="24"/>
     </row>
     <row r="71" ht="25" customHeight="1" spans="1:9">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="26">
+      <c r="A71" s="22"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="28">
         <v>47</v>
       </c>
-      <c r="F71" s="21" t="s">
+      <c r="F71" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="33"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="24"/>
     </row>
     <row r="72" ht="25" customHeight="1" spans="1:9">
-      <c r="A72" s="21"/>
-      <c r="B72" s="21"/>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="26">
+      <c r="A72" s="22"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="28">
         <v>48</v>
       </c>
-      <c r="F72" s="21" t="s">
+      <c r="F72" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="33"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="24"/>
     </row>
     <row r="73" ht="25" customHeight="1" spans="1:9">
-      <c r="A73" s="21"/>
-      <c r="B73" s="21"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="26">
+      <c r="A73" s="22"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="28">
         <v>49</v>
       </c>
-      <c r="F73" s="21" t="s">
+      <c r="F73" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="33"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="24"/>
     </row>
     <row r="74" ht="25" customHeight="1" spans="1:9">
-      <c r="A74" s="21"/>
-      <c r="B74" s="21" t="s">
+      <c r="A74" s="22"/>
+      <c r="B74" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="31" t="s">
+      <c r="C74" s="22"/>
+      <c r="D74" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="E74" s="26">
+      <c r="E74" s="28">
         <v>50</v>
       </c>
-      <c r="F74" s="21" t="s">
+      <c r="F74" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="G74" s="31" t="s">
+      <c r="G74" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="H74" s="31" t="s">
+      <c r="H74" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="I74" s="33" t="s">
+      <c r="I74" s="24" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="75" ht="25" customHeight="1" spans="1:9">
-      <c r="A75" s="21"/>
-      <c r="B75" s="21"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21" t="s">
+      <c r="A75" s="22"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="28">
         <v>51</v>
       </c>
-      <c r="F75" s="21" t="s">
+      <c r="F75" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="G75" s="31" t="s">
+      <c r="G75" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H75" s="31" t="s">
+      <c r="H75" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="I75" s="33"/>
+      <c r="I75" s="24"/>
     </row>
     <row r="76" ht="25" customHeight="1" spans="1:9">
-      <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="26">
+      <c r="A76" s="22"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="28">
         <v>52</v>
       </c>
-      <c r="F76" s="21" t="s">
+      <c r="F76" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="33"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="24"/>
     </row>
     <row r="77" ht="25" customHeight="1" spans="1:9">
-      <c r="A77" s="21"/>
-      <c r="B77" s="21"/>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="26">
+      <c r="A77" s="22"/>
+      <c r="B77" s="22"/>
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="28">
         <v>53</v>
       </c>
-      <c r="F77" s="21" t="s">
+      <c r="F77" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="33"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="24"/>
     </row>
     <row r="78" ht="25" customHeight="1" spans="1:9">
-      <c r="A78" s="21"/>
-      <c r="B78" s="21"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="26">
+      <c r="A78" s="22"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="28">
         <v>54</v>
       </c>
-      <c r="F78" s="21" t="s">
+      <c r="F78" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="33"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="24"/>
     </row>
     <row r="79" ht="25" customHeight="1" spans="1:9">
-      <c r="A79" s="23"/>
-      <c r="B79" s="31" t="s">
+      <c r="A79" s="25"/>
+      <c r="B79" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="C79" s="26" t="s">
+      <c r="C79" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="26"/>
-      <c r="H79" s="26"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28"/>
+      <c r="G79" s="28"/>
+      <c r="H79" s="28"/>
       <c r="I79" s="35"/>
     </row>
     <row r="80" ht="25" customHeight="1"/>
@@ -4197,7 +4211,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" ht="14.25" spans="1:8">
+    <row r="11" ht="14.25" spans="1:9">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -4207,7 +4221,7 @@
       <c r="G11" s="7"/>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" ht="14.25" spans="1:8">
+    <row r="12" ht="14.25" spans="1:9">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -4217,7 +4231,7 @@
       <c r="G12" s="7"/>
       <c r="H12" s="10"/>
     </row>
-    <row r="13" ht="14.25" spans="1:8">
+    <row r="13" ht="14.25" spans="1:9">
       <c r="A13" s="11"/>
       <c r="B13" s="11" t="s">
         <v>207</v>
@@ -4275,7 +4289,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:8">
+    <row r="16" ht="14.25" spans="1:9">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
         <v>191</v>
@@ -4287,7 +4301,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" ht="14.25" spans="1:8">
+    <row r="17" ht="14.25" spans="1:9">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -4299,7 +4313,7 @@
       <c r="G17" s="11"/>
       <c r="H17" s="13"/>
     </row>
-    <row r="18" ht="14.25" spans="1:8">
+    <row r="18" ht="14.25" spans="1:9">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4309,7 +4323,7 @@
       <c r="G18" s="11"/>
       <c r="H18" s="13"/>
     </row>
-    <row r="19" ht="14.25" spans="1:8">
+    <row r="19" ht="14.25" spans="1:9">
       <c r="A19" s="11"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4319,7 +4333,7 @@
       <c r="G19" s="11"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" ht="14.25" spans="1:8">
+    <row r="20" ht="14.25" spans="1:9">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4508,7 +4522,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="1:8">
+    <row r="29" ht="14.25" spans="1:9">
       <c r="A29" s="18"/>
       <c r="B29" s="18"/>
       <c r="C29" s="13"/>
@@ -4518,7 +4532,7 @@
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
     </row>
-    <row r="30" ht="14.25" spans="1:8">
+    <row r="30" ht="14.25" spans="1:9">
       <c r="A30" s="18"/>
       <c r="B30" s="18"/>
       <c r="C30" s="13"/>
@@ -4528,7 +4542,7 @@
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
     </row>
-    <row r="31" ht="14.25" spans="1:8">
+    <row r="31" ht="14.25" spans="1:9">
       <c r="A31" s="18"/>
       <c r="B31" s="18"/>
       <c r="C31" s="13"/>
@@ -4538,7 +4552,7 @@
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
     </row>
-    <row r="32" ht="14.25" spans="1:8">
+    <row r="32" ht="14.25" spans="1:9">
       <c r="A32" s="18"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -4548,7 +4562,7 @@
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
     </row>
-    <row r="33" ht="14.25" spans="1:8">
+    <row r="33" ht="14.25" spans="1:9">
       <c r="A33" s="18"/>
       <c r="B33" s="18"/>
       <c r="C33" s="13"/>
@@ -4558,7 +4572,7 @@
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
     </row>
-    <row r="34" ht="14.25" spans="1:8">
+    <row r="34" ht="14.25" spans="1:9">
       <c r="A34" s="15" t="s">
         <v>232</v>
       </c>
@@ -4570,7 +4584,7 @@
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
     </row>
-    <row r="35" ht="14.25" spans="1:8">
+    <row r="35" ht="14.25" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -4850,7 +4864,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:6">
+    <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="7" t="s">
         <v>241</v>
       </c>
@@ -4870,7 +4884,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:6">
+    <row r="10" ht="14.25" spans="1:7">
       <c r="A10" s="7" t="s">
         <v>241</v>
       </c>
@@ -4890,7 +4904,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:6">
+    <row r="11" ht="14.25" spans="1:7">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
@@ -4982,7 +4996,7 @@
       </c>
       <c r="G15" s="10"/>
     </row>
-    <row r="19" ht="14.25" spans="1:6">
+    <row r="19" ht="14.25" spans="1:7">
       <c r="A19" s="15" t="s">
         <v>232</v>
       </c>
@@ -4992,7 +5006,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" ht="14.25" spans="1:6">
+    <row r="20" ht="14.25" spans="1:7">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="4"/>
